--- a/database/Layers_Thickness.xlsx
+++ b/database/Layers_Thickness.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EDS\S2302 eQuest Automation\S2302.3 ML_eQuest_Automation\Test ML eQUEST\04 Modify &amp; Scale INPs\database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EDS\S2302 eQuest Automation\S2302.0 Batch_600_Per_Day\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C214DDA8-19A6-4503-BBC3-0BC8E1678F2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE07ADA-88F7-4B82-9C79-CD3E0A4982B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A4E3A5EE-C5FE-49D7-951A-33849BCC29B7}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="104">
   <si>
     <t>Name</t>
   </si>
@@ -343,6 +343,9 @@
   </si>
   <si>
     <t>ML_SCB200_EPS_50</t>
+  </si>
+  <si>
+    <t>ML_W_CP</t>
   </si>
 </sst>
 </file>
@@ -753,7 +756,7 @@
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="15" width="14.88671875" bestFit="1" customWidth="1"/>
@@ -878,7 +881,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
@@ -952,7 +955,7 @@
         <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
         <v>23</v>
@@ -1026,7 +1029,7 @@
         <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
         <v>23</v>
@@ -1100,7 +1103,7 @@
         <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="E5" t="s">
         <v>24</v>
@@ -1174,7 +1177,7 @@
         <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -1248,7 +1251,7 @@
         <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
         <v>98</v>
@@ -1322,7 +1325,7 @@
         <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
         <v>24</v>
@@ -1396,7 +1399,7 @@
         <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
         <v>24</v>
@@ -1470,7 +1473,7 @@
         <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="E10" t="s">
         <v>25</v>
@@ -1544,7 +1547,7 @@
         <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
         <v>25</v>
@@ -1618,7 +1621,7 @@
         <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
         <v>25</v>
@@ -1692,7 +1695,7 @@
         <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="E13" t="s">
         <v>99</v>
@@ -1766,7 +1769,7 @@
         <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="E14" t="s">
         <v>23</v>
@@ -1840,7 +1843,7 @@
         <v>73</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="E15" t="s">
         <v>24</v>
@@ -1914,7 +1917,7 @@
         <v>74</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="E16" t="s">
         <v>24</v>
@@ -1988,7 +1991,7 @@
         <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="E17" t="s">
         <v>23</v>
@@ -2062,7 +2065,7 @@
         <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="E18" t="s">
         <v>23</v>
@@ -2136,7 +2139,7 @@
         <v>77</v>
       </c>
       <c r="D19" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="E19" t="s">
         <v>24</v>
@@ -2210,7 +2213,7 @@
         <v>102</v>
       </c>
       <c r="D20" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="E20" t="s">
         <v>24</v>
@@ -2284,7 +2287,7 @@
         <v>72</v>
       </c>
       <c r="D21" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="E21" t="s">
         <v>100</v>
